--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -1,85 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Giresh\Documents\gnn-model-benchmark\results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9F08B6-28B1-4807-8C8D-027CA585F14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Dataset</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>Accuracy_Mean</t>
-  </si>
-  <si>
-    <t>Accuracy_STD</t>
-  </si>
-  <si>
-    <t>Folds</t>
-  </si>
-  <si>
-    <t>Training_Time</t>
-  </si>
-  <si>
-    <t>Parameters</t>
-  </si>
-  <si>
-    <t>Memory_MB</t>
-  </si>
-  <si>
-    <t>graph</t>
-  </si>
-  <si>
-    <t>gcn</t>
-  </si>
-  <si>
-    <t>mutag</t>
-  </si>
-  <si>
-    <t>0.75595 ± 0.07976</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -98,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,72 +408,810 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2">
-        <v>0.75595000000000001</v>
-      </c>
-      <c r="F2">
-        <v>7.9759999999999998E-2</v>
-      </c>
-      <c r="G2">
-        <v>6</v>
-      </c>
-      <c r="H2">
-        <v>3.85</v>
-      </c>
-      <c r="I2">
-        <v>322</v>
-      </c>
-      <c r="J2">
-        <v>342.07</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Hidden</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Dropout</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Weight_Decay</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Epochs</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Training_Time</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Memory_MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>gcn</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mutag</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>200</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.7389 ± 0.0975</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>386</v>
+      </c>
+      <c r="L2" t="n">
+        <v>357.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mutag</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>200</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.7442 ± 0.0958</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3590</v>
+      </c>
+      <c r="L3" t="n">
+        <v>379.39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>graphsage</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mutag</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.7602 ± 0.0839</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>674</v>
+      </c>
+      <c r="L4" t="n">
+        <v>359.32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mutag</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.7719 ± 0.1001</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1442</v>
+      </c>
+      <c r="L5" t="n">
+        <v>359.74</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gcn</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>proteins</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>200</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.6623 ± 0.0433</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>280.77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>258</v>
+      </c>
+      <c r="L6" t="n">
+        <v>403.61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>gat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>proteins</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>200</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.6793 ± 0.0508</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>674.4299999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2566</v>
+      </c>
+      <c r="L7" t="n">
+        <v>465.53</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>graphsage</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>proteins</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>200</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.6766 ± 0.0606</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>248.43</v>
+      </c>
+      <c r="K8" t="n">
+        <v>418</v>
+      </c>
+      <c r="L8" t="n">
+        <v>395.89</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>gin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>proteins</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>32</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>200</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.6829 ± 0.0396</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>331.38</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1314</v>
+      </c>
+      <c r="L9" t="n">
+        <v>400.85</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gcn</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>enzymes</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>200</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.3033 ± 0.0332</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>147.29</v>
+      </c>
+      <c r="K10" t="n">
+        <v>390</v>
+      </c>
+      <c r="L10" t="n">
+        <v>375.13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>enzymes</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>200</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.2667 ± 0.0453</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>341.86</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3602</v>
+      </c>
+      <c r="L11" t="n">
+        <v>426.58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>graphsage</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>enzymes</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>200</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.3133 ± 0.0371</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>126.34</v>
+      </c>
+      <c r="K12" t="n">
+        <v>678</v>
+      </c>
+      <c r="L12" t="n">
+        <v>382.38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>enzymes</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>32</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>200</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.3133 ± 0.0452</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>135.06</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1446</v>
+      </c>
+      <c r="L13" t="n">
+        <v>379.52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>gcn</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>nci1</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>32</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>200</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.6423 ± 0.0162</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1705.97</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1346</v>
+      </c>
+      <c r="L14" t="n">
+        <v>482.47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>gat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>nci1</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>32</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>200</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.6078 ± 0.0458</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3512.28</v>
+      </c>
+      <c r="K15" t="n">
+        <v>11270</v>
+      </c>
+      <c r="L15" t="n">
+        <v>501.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>graphsage</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nci1</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>32</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>200</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.6421 ± 0.0254</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2958.02</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2594</v>
+      </c>
+      <c r="L16" t="n">
+        <v>480.57</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>gin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nci1</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>32</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>200</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.6888 ± 0.0158</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2534.12</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2402</v>
+      </c>
+      <c r="L17" t="n">
+        <v>479.72</v>
       </c>
     </row>
   </sheetData>

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40.8</v>
+        <v>70.53</v>
       </c>
       <c r="K2" t="n">
         <v>386</v>
       </c>
       <c r="L2" t="n">
-        <v>357.4</v>
+        <v>368.34</v>
       </c>
     </row>
     <row r="3">

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,21 @@
           <t>Memory_MB</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,6 +538,9 @@
       <c r="L2" t="n">
         <v>368.34</v>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +587,9 @@
       <c r="L3" t="n">
         <v>379.39</v>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,6 +636,9 @@
       <c r="L4" t="n">
         <v>359.32</v>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -653,13 +677,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>38.58</v>
+        <v>95.19</v>
       </c>
       <c r="K5" t="n">
         <v>1442</v>
       </c>
       <c r="L5" t="n">
-        <v>359.74</v>
+        <v>359.78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8004</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7539</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.7347</v>
       </c>
     </row>
     <row r="6">
@@ -707,6 +740,9 @@
       <c r="L6" t="n">
         <v>403.61</v>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -753,6 +789,9 @@
       <c r="L7" t="n">
         <v>465.53</v>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -799,6 +838,9 @@
       <c r="L8" t="n">
         <v>395.89</v>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -845,6 +887,9 @@
       <c r="L9" t="n">
         <v>400.85</v>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -891,6 +936,9 @@
       <c r="L10" t="n">
         <v>375.13</v>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -937,6 +985,9 @@
       <c r="L11" t="n">
         <v>426.58</v>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -983,6 +1034,9 @@
       <c r="L12" t="n">
         <v>382.38</v>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1029,6 +1083,9 @@
       <c r="L13" t="n">
         <v>379.52</v>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1075,6 +1132,9 @@
       <c r="L14" t="n">
         <v>482.47</v>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1121,6 +1181,9 @@
       <c r="L15" t="n">
         <v>501.7</v>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1167,6 +1230,9 @@
       <c r="L16" t="n">
         <v>480.57</v>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1213,6 +1279,9 @@
       <c r="L17" t="n">
         <v>479.72</v>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,21 @@
           <t>F1</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Accuracy_Mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Accuracy_Std</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ROC_AUC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -530,17 +545,32 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>70.53</v>
+        <v>64.95</v>
       </c>
       <c r="K2" t="n">
-        <v>386</v>
+        <v>1442</v>
       </c>
       <c r="L2" t="n">
-        <v>368.34</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>367.05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6413</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.7126</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -590,6 +620,9 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -639,6 +672,9 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -677,13 +713,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>95.19</v>
+        <v>44.31</v>
       </c>
       <c r="K5" t="n">
         <v>1442</v>
       </c>
       <c r="L5" t="n">
-        <v>359.78</v>
+        <v>366.82</v>
       </c>
       <c r="M5" t="n">
         <v>0.8004</v>
@@ -693,6 +729,15 @@
       </c>
       <c r="O5" t="n">
         <v>0.7347</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.7719</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -743,6 +788,9 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -792,6 +840,9 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -841,6 +892,9 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -890,6 +944,9 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -939,6 +996,9 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -988,6 +1048,9 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1037,6 +1100,9 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1086,6 +1152,9 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1135,6 +1204,9 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,6 +1256,9 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1233,6 +1308,9 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1282,6 +1360,9 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,52 +459,47 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Accuracy_Mean</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Accuracy_Std</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ROC_AUC</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>Training_Time</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Parameters</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Memory_MB</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Recall</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Accuracy_Mean</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Accuracy_Std</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ROC_AUC</t>
         </is>
       </c>
     </row>
@@ -539,37 +534,32 @@
       <c r="H2" t="n">
         <v>200</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.7389 ± 0.0975</t>
-        </is>
+      <c r="I2" t="n">
+        <v>0.7126</v>
       </c>
       <c r="J2" t="n">
-        <v>64.95</v>
+        <v>0.0801</v>
       </c>
       <c r="K2" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6413</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="P2" t="n">
         <v>1442</v>
       </c>
-      <c r="L2" t="n">
-        <v>367.05</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.7074</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6413</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.7126</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0.0801</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
+        <v>361.19</v>
       </c>
     </row>
     <row r="3">
@@ -603,26 +593,33 @@
       <c r="H3" t="n">
         <v>200</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.7442 ± 0.0958</t>
-        </is>
+      <c r="I3" t="n">
+        <v>0.7442</v>
       </c>
       <c r="J3" t="n">
-        <v>75.40000000000001</v>
+        <v>0.0958</v>
       </c>
       <c r="K3" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6755</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6603</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="P3" t="n">
         <v>3590</v>
       </c>
-      <c r="L3" t="n">
-        <v>379.39</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>379.25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,26 +652,33 @@
       <c r="H4" t="n">
         <v>200</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.7602 ± 0.0839</t>
-        </is>
+      <c r="I4" t="n">
+        <v>0.7602</v>
       </c>
       <c r="J4" t="n">
-        <v>37.45</v>
+        <v>0.0839</v>
       </c>
       <c r="K4" t="n">
+        <v>0.7622</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7097</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="P4" t="n">
         <v>674</v>
       </c>
-      <c r="L4" t="n">
-        <v>359.32</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>360.05</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -707,37 +711,32 @@
       <c r="H5" t="n">
         <v>200</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.7719 ± 0.1001</t>
-        </is>
+      <c r="I5" t="n">
+        <v>0.7719</v>
       </c>
       <c r="J5" t="n">
-        <v>44.31</v>
+        <v>0.1001</v>
       </c>
       <c r="K5" t="n">
+        <v>0.8004</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7539</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7347</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="P5" t="n">
         <v>1442</v>
       </c>
-      <c r="L5" t="n">
-        <v>366.82</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8004</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.7539</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.7347</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.7719</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0.1001</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
+        <v>359.85</v>
       </c>
     </row>
     <row r="6">
@@ -771,26 +770,33 @@
       <c r="H6" t="n">
         <v>200</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.6623 ± 0.0433</t>
-        </is>
+      <c r="I6" t="n">
+        <v>0.6811</v>
       </c>
       <c r="J6" t="n">
-        <v>280.77</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>258</v>
+        <v>0.6841</v>
       </c>
       <c r="L6" t="n">
-        <v>403.61</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+        <v>0.6476</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6414</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>442.15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1314</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>409.09</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -823,26 +829,33 @@
       <c r="H7" t="n">
         <v>200</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.6793 ± 0.0508</t>
-        </is>
+      <c r="I7" t="n">
+        <v>0.6793</v>
       </c>
       <c r="J7" t="n">
-        <v>674.4299999999999</v>
+        <v>0.0508</v>
       </c>
       <c r="K7" t="n">
+        <v>0.6714</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6657999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6621</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>680.65</v>
+      </c>
+      <c r="P7" t="n">
         <v>2566</v>
       </c>
-      <c r="L7" t="n">
-        <v>465.53</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>465.77</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -875,26 +888,33 @@
       <c r="H8" t="n">
         <v>200</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.6766 ± 0.0606</t>
-        </is>
+      <c r="I8" t="n">
+        <v>0.6766</v>
       </c>
       <c r="J8" t="n">
-        <v>248.43</v>
+        <v>0.0606</v>
       </c>
       <c r="K8" t="n">
+        <v>0.6723</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.6419</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>247.66</v>
+      </c>
+      <c r="P8" t="n">
         <v>418</v>
       </c>
-      <c r="L8" t="n">
-        <v>395.89</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>397.34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -927,26 +947,33 @@
       <c r="H9" t="n">
         <v>200</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.6829 ± 0.0396</t>
-        </is>
+      <c r="I9" t="n">
+        <v>0.6829</v>
       </c>
       <c r="J9" t="n">
-        <v>331.38</v>
+        <v>0.0396</v>
       </c>
       <c r="K9" t="n">
+        <v>0.6771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6657999999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.6629</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>327.42</v>
+      </c>
+      <c r="P9" t="n">
         <v>1314</v>
       </c>
-      <c r="L9" t="n">
-        <v>400.85</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>400.48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -979,26 +1006,33 @@
       <c r="H10" t="n">
         <v>200</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.3033 ± 0.0332</t>
-        </is>
+      <c r="I10" t="n">
+        <v>0.3017</v>
       </c>
       <c r="J10" t="n">
-        <v>147.29</v>
+        <v>0.0376</v>
       </c>
       <c r="K10" t="n">
-        <v>390</v>
+        <v>0.2957</v>
       </c>
       <c r="L10" t="n">
-        <v>375.13</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+        <v>0.2978</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="O10" t="n">
+        <v>187.27</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1446</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>382.64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1031,26 +1065,33 @@
       <c r="H11" t="n">
         <v>200</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.2667 ± 0.0453</t>
-        </is>
+      <c r="I11" t="n">
+        <v>0.2667</v>
       </c>
       <c r="J11" t="n">
-        <v>341.86</v>
+        <v>0.0453</v>
       </c>
       <c r="K11" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="O11" t="n">
+        <v>338.44</v>
+      </c>
+      <c r="P11" t="n">
         <v>3602</v>
       </c>
-      <c r="L11" t="n">
-        <v>426.58</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>427.09</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1083,26 +1124,33 @@
       <c r="H12" t="n">
         <v>200</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.3133 ± 0.0371</t>
-        </is>
+      <c r="I12" t="n">
+        <v>0.3133</v>
       </c>
       <c r="J12" t="n">
-        <v>126.34</v>
+        <v>0.0371</v>
       </c>
       <c r="K12" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6546999999999999</v>
+      </c>
+      <c r="O12" t="n">
+        <v>125.88</v>
+      </c>
+      <c r="P12" t="n">
         <v>678</v>
       </c>
-      <c r="L12" t="n">
-        <v>382.38</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>383.79</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1135,26 +1183,33 @@
       <c r="H13" t="n">
         <v>200</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.3133 ± 0.0452</t>
-        </is>
+      <c r="I13" t="n">
+        <v>0.3133</v>
       </c>
       <c r="J13" t="n">
-        <v>135.06</v>
+        <v>0.0452</v>
       </c>
       <c r="K13" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6689000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>134.89</v>
+      </c>
+      <c r="P13" t="n">
         <v>1446</v>
       </c>
-      <c r="L13" t="n">
-        <v>379.52</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>380.44</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1187,26 +1242,33 @@
       <c r="H14" t="n">
         <v>200</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.6423 ± 0.0162</t>
-        </is>
+      <c r="I14" t="n">
+        <v>0.6333</v>
       </c>
       <c r="J14" t="n">
-        <v>1705.97</v>
+        <v>0.0179</v>
       </c>
       <c r="K14" t="n">
-        <v>1346</v>
+        <v>0.6511</v>
       </c>
       <c r="L14" t="n">
-        <v>482.47</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+        <v>0.6324</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.6202</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2032.45</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2402</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>484.59</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1239,26 +1301,33 @@
       <c r="H15" t="n">
         <v>200</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.6078 ± 0.0458</t>
-        </is>
+      <c r="I15" t="n">
+        <v>0.6078</v>
       </c>
       <c r="J15" t="n">
-        <v>3512.28</v>
+        <v>0.0458</v>
       </c>
       <c r="K15" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6094000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2936.95</v>
+      </c>
+      <c r="P15" t="n">
         <v>11270</v>
       </c>
-      <c r="L15" t="n">
-        <v>501.7</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>470.4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1291,26 +1360,33 @@
       <c r="H16" t="n">
         <v>200</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.6421 ± 0.0254</t>
-        </is>
+      <c r="I16" t="n">
+        <v>0.6421</v>
       </c>
       <c r="J16" t="n">
-        <v>2958.02</v>
+        <v>0.0254</v>
       </c>
       <c r="K16" t="n">
+        <v>0.6569</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.6346000000000001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1240.12</v>
+      </c>
+      <c r="P16" t="n">
         <v>2594</v>
       </c>
-      <c r="L16" t="n">
-        <v>480.57</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>482.97</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1343,26 +1419,33 @@
       <c r="H17" t="n">
         <v>200</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.6888 ± 0.0158</t>
-        </is>
+      <c r="I17" t="n">
+        <v>0.6888</v>
       </c>
       <c r="J17" t="n">
-        <v>2534.12</v>
+        <v>0.0158</v>
       </c>
       <c r="K17" t="n">
+        <v>0.6952</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6878</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6851</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1971.94</v>
+      </c>
+      <c r="P17" t="n">
         <v>2402</v>
       </c>
-      <c r="L17" t="n">
-        <v>479.72</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>481.18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1447,6 +1447,65 @@
         <v>481.18</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>gcn</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MUTAG</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>32</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>200</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.6977</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.6567</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.7419</v>
+      </c>
+      <c r="O18" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1506</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>362.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -1479,31 +1479,31 @@
         <v>200</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7175</v>
+        <v>0.7237</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1106</v>
+        <v>0.0833</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6977</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6803</v>
+        <v>0.6526</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6567</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7419</v>
+        <v>0.7998</v>
       </c>
       <c r="O18" t="n">
-        <v>52.67</v>
+        <v>14.47</v>
       </c>
       <c r="P18" t="n">
         <v>1506</v>
       </c>
       <c r="Q18" t="n">
-        <v>362.16</v>
+        <v>361.8</v>
       </c>
     </row>
   </sheetData>

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -1497,13 +1497,13 @@
         <v>0.7998</v>
       </c>
       <c r="O18" t="n">
-        <v>14.47</v>
+        <v>26.86</v>
       </c>
       <c r="P18" t="n">
         <v>1506</v>
       </c>
       <c r="Q18" t="n">
-        <v>361.8</v>
+        <v>380.63</v>
       </c>
     </row>
   </sheetData>

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -535,31 +535,31 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7126</v>
+        <v>0.7178</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0801</v>
+        <v>0.0798</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7074</v>
+        <v>0.73</v>
       </c>
       <c r="L2" t="n">
-        <v>0.64</v>
+        <v>0.6454</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6413</v>
+        <v>0.6392</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.8096</v>
       </c>
       <c r="O2" t="n">
-        <v>54.94</v>
+        <v>15.18</v>
       </c>
       <c r="P2" t="n">
-        <v>1442</v>
+        <v>1506</v>
       </c>
       <c r="Q2" t="n">
-        <v>361.19</v>
+        <v>380.24</v>
       </c>
     </row>
     <row r="3">

--- a/results/graph_results.xlsx
+++ b/results/graph_results.xlsx
@@ -535,31 +535,31 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7178</v>
+        <v>0.7608</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0798</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.73</v>
+        <v>0.7523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6454</v>
+        <v>0.7013</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6392</v>
+        <v>0.7046</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8096</v>
+        <v>0.7936</v>
       </c>
       <c r="O2" t="n">
-        <v>15.18</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="P2" t="n">
         <v>1506</v>
       </c>
       <c r="Q2" t="n">
-        <v>380.24</v>
+        <v>421.56</v>
       </c>
     </row>
     <row r="3">
@@ -594,31 +594,31 @@
         <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7442</v>
+        <v>0.7023</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0958</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.713</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6755</v>
+        <v>0.5968</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6603</v>
+        <v>0.5692</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.7975</v>
       </c>
       <c r="O3" t="n">
-        <v>75.78</v>
+        <v>19.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3590</v>
+        <v>1634</v>
       </c>
       <c r="Q3" t="n">
-        <v>379.25</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
@@ -653,31 +653,31 @@
         <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7602</v>
+        <v>0.7441</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0839</v>
+        <v>0.0756</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7622</v>
+        <v>0.7333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7097</v>
+        <v>0.6933</v>
       </c>
       <c r="M4" t="n">
-        <v>0.707</v>
+        <v>0.6906</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.7978</v>
       </c>
       <c r="O4" t="n">
-        <v>37.05</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>674</v>
+        <v>2754</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.05</v>
+        <v>419.21</v>
       </c>
     </row>
     <row r="5">
@@ -712,31 +712,31 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7719</v>
+        <v>0.8035</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1001</v>
+        <v>0.0664</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8004</v>
+        <v>0.8174</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7539</v>
+        <v>0.7776</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7347</v>
+        <v>0.7685</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.9018</v>
       </c>
       <c r="O5" t="n">
-        <v>38.24</v>
+        <v>11.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1442</v>
+        <v>3618</v>
       </c>
       <c r="Q5" t="n">
-        <v>359.85</v>
+        <v>419.57</v>
       </c>
     </row>
     <row r="6">
@@ -771,31 +771,31 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6811</v>
+        <v>0.6775</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.035</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6841</v>
+        <v>0.6798</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6476</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6414</v>
+        <v>0.6489</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.7016</v>
       </c>
       <c r="O6" t="n">
-        <v>442.15</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1314</v>
+        <v>1378</v>
       </c>
       <c r="Q6" t="n">
-        <v>409.09</v>
+        <v>437.29</v>
       </c>
     </row>
     <row r="7">
@@ -830,31 +830,31 @@
         <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6793</v>
+        <v>0.655</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0508</v>
+        <v>0.0423</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6714</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6414</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6621</v>
+        <v>0.6365</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.6865</v>
       </c>
       <c r="O7" t="n">
-        <v>680.65</v>
+        <v>119.36</v>
       </c>
       <c r="P7" t="n">
-        <v>2566</v>
+        <v>1506</v>
       </c>
       <c r="Q7" t="n">
-        <v>465.77</v>
+        <v>444.73</v>
       </c>
     </row>
     <row r="8">
@@ -889,31 +889,31 @@
         <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6766</v>
+        <v>0.6838</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0606</v>
+        <v>0.058</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6723</v>
+        <v>0.6745</v>
       </c>
       <c r="L8" t="n">
-        <v>0.641</v>
+        <v>0.6621</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6419</v>
+        <v>0.6636</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.7052</v>
       </c>
       <c r="O8" t="n">
-        <v>247.66</v>
+        <v>57.06</v>
       </c>
       <c r="P8" t="n">
-        <v>418</v>
+        <v>2498</v>
       </c>
       <c r="Q8" t="n">
-        <v>397.34</v>
+        <v>434.43</v>
       </c>
     </row>
     <row r="9">
@@ -948,31 +948,31 @@
         <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6829</v>
+        <v>0.6892</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0396</v>
+        <v>0.0536</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6771</v>
+        <v>0.6896</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6667</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6629</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.7125</v>
       </c>
       <c r="O9" t="n">
-        <v>327.42</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>1314</v>
+        <v>3490</v>
       </c>
       <c r="Q9" t="n">
-        <v>400.48</v>
+        <v>433.43</v>
       </c>
     </row>
     <row r="10">
@@ -1007,31 +1007,31 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3017</v>
+        <v>0.295</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0376</v>
+        <v>0.0683</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2957</v>
+        <v>0.2826</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2978</v>
+        <v>0.295</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2631</v>
+        <v>0.2633</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6474</v>
+        <v>0.6535</v>
       </c>
       <c r="O10" t="n">
-        <v>187.27</v>
+        <v>48.99</v>
       </c>
       <c r="P10" t="n">
-        <v>1446</v>
+        <v>1510</v>
       </c>
       <c r="Q10" t="n">
-        <v>382.64</v>
+        <v>428.86</v>
       </c>
     </row>
     <row r="11">
@@ -1066,31 +1066,31 @@
         <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2667</v>
+        <v>0.2217</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0453</v>
+        <v>0.0633</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2419</v>
+        <v>0.1931</v>
       </c>
       <c r="L11" t="n">
-        <v>0.272</v>
+        <v>0.2217</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2268</v>
+        <v>0.1724</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6141</v>
       </c>
       <c r="O11" t="n">
-        <v>338.44</v>
+        <v>61.36</v>
       </c>
       <c r="P11" t="n">
-        <v>3602</v>
+        <v>1638</v>
       </c>
       <c r="Q11" t="n">
-        <v>427.09</v>
+        <v>429.22</v>
       </c>
     </row>
     <row r="12">
@@ -1125,31 +1125,31 @@
         <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3133</v>
+        <v>0.32</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0371</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3022</v>
+        <v>0.3252</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3172</v>
+        <v>0.32</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2871</v>
+        <v>0.2921</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6476</v>
       </c>
       <c r="O12" t="n">
-        <v>125.88</v>
+        <v>35.22</v>
       </c>
       <c r="P12" t="n">
-        <v>678</v>
+        <v>2630</v>
       </c>
       <c r="Q12" t="n">
-        <v>383.79</v>
+        <v>427.39</v>
       </c>
     </row>
     <row r="13">
@@ -1184,31 +1184,31 @@
         <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3133</v>
+        <v>0.305</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0452</v>
+        <v>0.0916</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3205</v>
+        <v>0.3326</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3161</v>
+        <v>0.305</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2836</v>
+        <v>0.2904</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6542</v>
       </c>
       <c r="O13" t="n">
-        <v>134.89</v>
+        <v>33.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1446</v>
+        <v>3622</v>
       </c>
       <c r="Q13" t="n">
-        <v>380.44</v>
+        <v>426.85</v>
       </c>
     </row>
     <row r="14">
@@ -1243,31 +1243,31 @@
         <v>200</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6333</v>
+        <v>0.655</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0179</v>
+        <v>0.0244</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6511</v>
+        <v>0.6697</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6324</v>
+        <v>0.6548</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6202</v>
+        <v>0.6469</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>2032.45</v>
+        <v>344.36</v>
       </c>
       <c r="P14" t="n">
-        <v>2402</v>
+        <v>2466</v>
       </c>
       <c r="Q14" t="n">
-        <v>484.59</v>
+        <v>476.25</v>
       </c>
     </row>
     <row r="15">
@@ -1302,31 +1302,31 @@
         <v>200</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6078</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0458</v>
+        <v>0.047</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6498</v>
+        <v>0.6267</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.5999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.574</v>
+        <v>0.5688</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.6687</v>
       </c>
       <c r="O15" t="n">
-        <v>2936.95</v>
+        <v>388.34</v>
       </c>
       <c r="P15" t="n">
-        <v>11270</v>
+        <v>2594</v>
       </c>
       <c r="Q15" t="n">
-        <v>470.4</v>
+        <v>479.76</v>
       </c>
     </row>
     <row r="16">
@@ -1361,31 +1361,31 @@
         <v>200</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6421</v>
+        <v>0.656</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0254</v>
+        <v>0.0236</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6569</v>
+        <v>0.675</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6562</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6461</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.7408</v>
       </c>
       <c r="O16" t="n">
-        <v>1240.12</v>
+        <v>535.96</v>
       </c>
       <c r="P16" t="n">
-        <v>2594</v>
+        <v>4674</v>
       </c>
       <c r="Q16" t="n">
-        <v>482.97</v>
+        <v>465.52</v>
       </c>
     </row>
     <row r="17">
@@ -1420,31 +1420,31 @@
         <v>200</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6888</v>
+        <v>0.6535</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0158</v>
+        <v>0.0404</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6952</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6878</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6851</v>
+        <v>0.6357</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.7415</v>
       </c>
       <c r="O17" t="n">
-        <v>1971.94</v>
+        <v>532.0700000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>2402</v>
+        <v>4578</v>
       </c>
       <c r="Q17" t="n">
-        <v>481.18</v>
+        <v>462.74</v>
       </c>
     </row>
     <row r="18">
